--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1104QA5100</t>
+          <t>VGORD1119QA6500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DD9293-100-7</t>
+          <t>924156-100-S</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1119QA6500</t>
+          <t>VGORD1120QA7600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1120QA7600</t>
+          <t>VGORD1218QA9600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1218QA9600</t>
+          <t>VGORD1223QA9320</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -466,8 +466,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1081</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -476,27 +478,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VGORD1223QA9320</t>
+          <t>81ORD0113QA2910</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Z014</t>
+          <t>Z003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0008006063</t>
+          <t>0005000049</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>924156-100-S</t>
+          <t>130690-104-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81ORD0113QA2910</t>
+          <t>8101208380</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8101208380</t>
+          <t>V101222530</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>130690-104-16</t>
+          <t>899371-091-M</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V101222530</t>
+          <t>V101273850</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/J30/Output_files/Order_Creation_Report.xlsx
+++ b/J30/Output_files/Order_Creation_Report.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V101273850</t>
+          <t>V102044280</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,17 +488,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0005000049</t>
+          <t>0005000004</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>899371-091-M</t>
+          <t>343738-031-1.5Y</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
